--- a/raw_data/faq.xlsx
+++ b/raw_data/faq.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Master\HK4\demo\streamlit\chatbotbk\raw_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C63FFB9-B2AB-4252-BEF3-F76797D3A33F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F49F43E9-C723-473C-A571-5AE22BD914BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7180" yWindow="5590" windowWidth="19100" windowHeight="12340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,210 +25,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>question</t>
-  </si>
-  <si>
-    <t>Khối lượng chương trình đào tạo thạc sĩ bao nhiêu chỉ?</t>
-  </si>
-  <si>
-    <t>Thời gian đào tạo thạc sĩ bao nhiêu lâu?</t>
-  </si>
-  <si>
-    <t>Yêu cầu trình độ tiếng Anh để tốt nghiệp đối với thạc sĩ?</t>
-  </si>
-  <si>
-    <t>Cho tôi hỏi điểm R là điểm gì?</t>
-  </si>
-  <si>
-    <t>Chương trình đào tạo thạc sĩ ứng dụng là gì?</t>
-  </si>
-  <si>
-    <t>Tổng kết điểm môn học bao nhiêu là đạt đối với thạc sĩ?</t>
-  </si>
-  <si>
-    <t>Cho tôi hỏi về tiêu chuẩn dành cho huy chương vàng?</t>
-  </si>
-  <si>
-    <t>Điều kiện học viên đăng ký học chương trình song ngành là gì?</t>
-  </si>
-  <si>
-    <t>Thời hạn nộp đơn xin nhận điểm R là khi nào?</t>
-  </si>
-  <si>
-    <t>Số lượng tín chỉ đăng ký tối đa trong một học kỳ đối với thạc sĩ?</t>
-  </si>
-  <si>
-    <t>Nội dung chương trình đào tạo thạc sĩ gồm mấy phần?</t>
-  </si>
-  <si>
-    <t>Đăng ký môn học tự chọn quy định như thế nào?</t>
-  </si>
-  <si>
-    <t>Điều kiện được bảo vệ luận văn thạc sĩ?</t>
-  </si>
-  <si>
-    <t>Có những loại chương trình đào tạo thạc sĩ nào?</t>
-  </si>
-  <si>
-    <t>Đăng ký chương trình đào tạo thạc sĩ nghiên cứu chuyên sâu cần những điều kiện gì?</t>
-  </si>
-  <si>
-    <t>Quy định về số tín chỉ của chương trình đào tạo ngành thứ hai như thế nào?</t>
-  </si>
-  <si>
-    <t>Điều chỉnh loại chương trình đào tạo thạc sĩ như thế nào?</t>
-  </si>
-  <si>
-    <t>Thay đổi cán bộ hướng dẫn luận văn thạc sĩ có được không?</t>
-  </si>
-  <si>
-    <t>Có bằng tốt nghiệp nước ngoài sử dụng tiếng Anh, có được miễn bằng ngoại ngữ để tốt nghiệp thạc sĩ không?</t>
-  </si>
-  <si>
-    <t>Yêu cầu bảo vệ luận văn thạc sĩ đối với chương trình thạc sĩ nghiên cứu chuyên sâu như thế nào?</t>
-  </si>
-  <si>
-    <t>Điều kiện công nhận học viên tốt nghiệp?</t>
-  </si>
-  <si>
-    <t>Điểm A quy đổi qua thang điểm 10 như thế nào?</t>
   </si>
   <si>
     <t>answer</t>
   </si>
   <si>
-    <t>Theo quy định của Trường ĐH Bách Khoa Tp.HCM, chương trình đào tạo thạc sĩ có khối lượng 60 tín chỉ.</t>
-  </si>
-  <si>
-    <t>Theo quy định của Trường ĐH Bách Khoa Tp.HCM, thời gian đào tạo chính thức của khóa đào tạo thạc sĩ là 2 năm.Thời gian đào tạo của học viên căn cứ theo thời điểm chính thức bắt đầu của khóa học, được ghi rõ trong quyết định công nhận học viên.</t>
-  </si>
-  <si>
-    <t>Theo quy định của Trường ĐH Bách Khoa Tp.HCM, để tốt nghiệp thạc sĩ cần có chứng chỉ trình độ ngoại ngữ tối thiểu tương đương cấp B2 theo CEFR với yêu cầu Tiếng Anh cụ thể như sau: Chứng chỉ TOEFL iBT 46; TOEIC 4 kỹ năng (Nghe: 400, Đọc: 385, Nói: 160, Viết: 150); IELTS 5.5; Cambridge Assessment English: 160.</t>
-  </si>
-  <si>
-    <t>Theo quy định của Trường ĐH Bách Khoa Tp.HCM, điểm R là điểm học phần được miễn học và công nhận tín chỉ.</t>
-  </si>
-  <si>
-    <t>Theo quy định của Trường ĐH Bách Khoa Tp.HCM, chương trình đào tạo thạc sĩ ứng dụng là chương trình giúp học viên nâng cao kiến thức chuyên môn và kỹ năng hoạt động nghề nghiệp; có năng lực làm việc độc lập, sáng tạo; có khả năng thiết kế sản phẩm, ứng dụng kết quả nghiên cứu, phát hiện và tổ chức thực hiện các công việc phức tạp trong hoạt động chuyên môn nghề nghiệp.</t>
-  </si>
-  <si>
-    <t>Theo quy định của Trường ĐH Bách Khoa Tp.HCM, điểm tổng kết môn học là điểm trung bình theo trọng số các điểm đánh giá thành phần lấy đến 1 chữ số thập phân. Môn học được xem là đạt yêu cầu khi điểm tổng kết đạt từ 5,5 trở lên.</t>
-  </si>
-  <si>
-    <t>Theo quy định của Trường ĐH Bách Khoa Tp.HCM, tiêu chuẩn dành cho huy chương vàng được quy định như sau:
-- Xếp loại học lực khi tốt nghiệp (xếp loại tốt nghiệp) Giỏi trở lên;
-- Người học của Chương trình Chất lượng cao, Tiên tiến phải có chứng chỉ quốc tế tương đương IELTS từ 6.5 trở lên;
-- Không học lại bất kỳ học phần nào trong chương trình đào tạo.</t>
-  </si>
-  <si>
-    <t>Theo quy định của Trường ĐH Bách Khoa Tp.HCM, điều kiện học viên đăng ký học chương trình song ngành là:
-- Học viên đang học chương trình đào tạo theo hình thức chính quy; 
-- Học viên đã hoàn thành năm học đầu tiên và tích lũy được tối thiểu 30 tín chỉ của chương trình đào tạo ngành thứ nhất với điểm trung bình tích lũy từ 6,5 trở lên theo thang điểm 10.</t>
-  </si>
-  <si>
-    <t>Theo quy định của Trường ĐH Bách Khoa Tp.HCM, thời hạn nộp đơn xin nhận điểm R là 10 tuần kể từ ngày bắt đầu học kỳ tương ứng, trừ các trường hợp có lý do bất khả kháng (có minh chứng) trong vòng 7 ngày sau khi thi.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-Theo quy định của Trường ĐH Bách Khoa Tp.HCM, để đảm bảo có đủ thời gian hoàn tất khối lượng học tập, học viên không được đăng ký quá 20 tín chỉ trong một học kỳ. Riêng ở học kỳ thực hiện Luận văn Thạc sĩ, Đồ án tốt nghiệp, học viên chỉ được đăng ký học thêm tối đa 6 tín chỉ các môn học khác;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-Theo quy định của Trường ĐH Bách Khoa Tp.HCM, nội dung chương trình đào tạo thạc sĩ gồm 5 phần:
-- Phần 1 – Khối kiến thức chung, gồm các môn Triết học, Ngoại ngữ và các môn học chung. Môn ngoại ngữ là môn học điều kiện và kết quả đánh giá môn ngoại ngữ không tính trong điểm trung bình tích lũy; 
-- Phần 2 – Khối kiến thức cơ sở ngành; 
-- Phần 3 – Khối kiến thức bắt buộc chuyên ngành; 
-- Phần 4 – Khối kiến thức tự chọn chuyên ngành;
-- Phần 5 – Luận văn Thạc Sĩ (LVThS), Đồ án tốt nghiệp (ĐATN), thực tập, các
-chuyên đề nghiên cứu khoa học.</t>
-  </si>
-  <si>
-    <t>Theo quy định của Trường ĐH Bách Khoa Tp.HCM, đăng ký môn học tự chọn quy định như sau:
-- Khi đăng ký môn học, học viên được quyền chọn môn học tự chọn từ tất cả các
-môn học được lập kế hoạch giảng dạy ở học kỳ tương ứng;
-- Học viên có quyền chọn tối đa 6 tín chỉ từ Chương trình đào tạo của ngành khác
-nếu được sự đồng ý của Khoa; có quyền đăng ký môn học khác thay thế nếu
-không đạt điểm môn học tự chọn đã đăng ký.</t>
-  </si>
-  <si>
-    <t>Theo quy định của Trường ĐH Bách Khoa Tp.HCM, điều kiện được bảo vệ Luận văn Thạc sĩ, Đồ án tốt nghiệp quy định như sau:
-1. Nộp luận văn, đồ án đúng thời hạn theo quyết định giao đề tài. Học viên nộp tối thiểu 5 thuyết minh luận văn, 3 thuyết minh đồ án (bìa mềm), có xác nhận đã hoàn thành luận văn của Cán bộ hướng dẫn trên tờ Nhiệm vụ Luận văn Thạc sĩ, Đồ án tốt nghiệp cho Bộ môn.
-2. Học viên hoàn thành Chương trình đào tạo, có điểm trung bình tích lũy các môn học trong Chương trình đào tạo đạt từ 5,5 trở lên.
-3. Không bị truy cứu trách nhiệm hình sự và không trong thời gian bị kỷ luật, đình chỉ học tập; không bị tố cáo theo quy định của pháp luật về nội dung khoa học trong luận văn.
-4. Được nợ tối đa 1 môn (tối đa 4 tín chỉ).
-5. Luận văn, đồ án được ít nhất 1 cán bộ phản biện đồng ý cho phép bảo vệ.</t>
-  </si>
-  <si>
-    <t>Theo quy định của Trường ĐH Bách Khoa Tp.HCM, có 3 loại chương trình đào tạo thạc sĩ: thạc sĩ ứng dụng, thạc sĩ nghiên cứu và thạc sĩ nghiên cứu chuyên sâu.</t>
-  </si>
-  <si>
-    <t>Theo quy định của Trường ĐH Bách Khoa Tp.HCM, để được đăng ký học Chương trình đào tạo nghiên cứu chhuyên sâu, học viên phải đáp ứng đầy đủ các điều kiện sau:
-- Đăng ký học Chương trình đào tạo theo phương thức nghiên cứu trong thời gian đăng ký môn học của học kỳ;
-- Có giấy cam kết đảm bảo tối thiểu 50% thời gian làm việc tại bộ môn đào tạo/ Phòng thí nghiệm của Trường;
-- Tham gia các hoạt động đào tạo và nghiên cứu khoa học tại Trường Đại học Bách Khoa;
-- Tốt nghiệp đại học loại khá trở lên hoặc có công bố khoa học liên quan đến lĩnh vực sẽ học tập, nghiên cứu;
-- Có giấy chấp thuận hướng dẫn Luận văn Thạc sĩ của cán bộ hướng dẫn (CBHD), có xác nhận của bộ môn đào tạo/ Phòng thí nghiệm và Khoa đảm bảo điều kiện nghiên cứu cho học viên.
-- Thực hiện thủ tục đăng ký học chương trình thạc sĩ nghiên cứu chuyên sâu ngay từ đầu khóa học.</t>
-  </si>
-  <si>
-    <t>Theo quy định của Trường ĐH Bách Khoa Tp.HCM, số tín chỉ của chương trình đào tạo ngành thứ hai như sau:
-- Đối với ngành gần: khối lượng môn học tối thiểu 15 tín chỉ và luận văn, đồ án tốt nghiệp;
-- Đối với ngành khác: khối lượng môn học tối thiểu 30 tín chỉ và luận văn, đồ án tốt nghiệp;
-- Tổng khối lượng tín chỉ của chương trình ngành đào tạo thứ hai (bao gồm các tín chỉ trùng nhau và được công nhận tương đương giữa hai chương trình song ngành) là 60 tín chỉ.</t>
-  </si>
-  <si>
-    <t>Theo quy định của Trường ĐH Bách Khoa Tp.HCM, học viên có quyền điều chỉnh loại Chương trình đào tạo trong quá trình học tập của mình nếu đáp ứng các yêu cầu sau: 
-- Không trong thời gian bị kỷ luật từ cảnh cáo trở lên; 
-- Học viên không đang học ở học kỳ cuối của chương trình đào tạo hoặc đang thực hiện luận văn thạc sĩ.
-Để được điều chỉnh loại Chương trình đào tạo, học viên phải nộp đơn xin điều chỉnh có sự chấp thuận của Khoa và gửi Phòng Đào tạo sau đại học vào đầu học kỳ (tại thời điểm đăng ký môn học bổ sung).</t>
-  </si>
-  <si>
-    <t>Theo quy định của Trường ĐH Bách Khoa Tp.HCM, được phép thay đổi Cán bộ hướng dẫn luận văn thạc sĩ. Học viên phải có đơn được sự chấp thuận của Cán bộ hướng dẫn chính và phụ (nếu có), Bộ môn đào tạo, Khoa quản lý ngành và nộp cho Phòng Đào tạo sau đại học trong 6 tuần đầu tiên của học kỳ thực hiện luận văn thạc sĩ, đồ án tốt nghiệp.</t>
-  </si>
-  <si>
-    <t>Theo quy định của Trường ĐH Bách Khoa Tp.HCM, học viên được công nhận đủ trình độ ngoại ngữ để tốt nghiệp chương trình đào tạo trình độ thạc sĩ khi có bằng tốt nghiệp đại học, thạc sĩ hoặc tiến sĩ được đào tạo toàn thời gian tại nước ngoài mà ngôn ngữ sử dụng trong đào tạo là một trong các ngôn ngữ Anh, Pháp, Nga, Đức, Trung, Nhật, Hàn;</t>
-  </si>
-  <si>
-    <t>Theo quy định của Trường ĐH Bách Khoa Tp.HCM, để được bảo vệ Luận văn Thạc sĩ, học viên chương trình nghiên cứu chuyên sâu phải
-là tác giả chính (tác giả đứng đầu hoặc tác giả liên hệ) của ít nhất một công bố khoa
-học liên quan đến nội dung luận văn, được chấp nhận đăng trong danh mục Web of
-Science (WoS)/Scopus trong quá trình đào tạo. Bên cạnh đó, học viên cần sử dụng
-địa chỉ thư điện tử Trường Đại học Bách Khoa trong các công bố khoa học liên quan
-đến nội dung luận văn.</t>
-  </si>
-  <si>
-    <t>Theo quy định của Trường ĐH Bách Khoa Tp.HCM, học viên được công nhận tốt nghiệp nếu hội đủ các điều kiện sau:
-- Hoàn thành Chương trình đào tạo ngành trong thời hạn học tập của khóa đào tạo liên quan;
-- Đủ điều kiện ngoại ngữ.
-- Đã nộp luận văn thạc sĩ, đồ án tốt nghiệp được Hội đồng đánh giá đạt yêu cầu trở
-lên, có xác nhận của người hướng dẫn và chủ tịch hội đồng về việc luận văn, đồ
-án đã được chỉnh sửa theo kết luận của Hội đồng;
-- Trường hợp Học viên học Chương trình đào tạo theo phương thức nghiên cứu đã
-bảo vệ thành công Luận văn thạc sĩ nhưng không thể hoàn thành Báo cáo khoa
-học, để được cấp bằng thạc sĩ, học viên phải hoàn tất đầy đủ số tín chỉ môn học
-quy định đối với Chương trình đào tạo theo phương thức ứng dụng trong thời hạn
-của khóa đào tạo liên quan.</t>
-  </si>
-  <si>
-    <t>Theo quy định của Trường ĐH Bách Khoa Tp.HCM, điểm A được quy đổi theo thang điểm 10 từ 8,5 đến 9,4;</t>
-  </si>
-  <si>
-    <t>Xin chào, tôi là một trợ lý hỗ trợ giải đáp các thắc mắc về quy định học vụ của trường ĐH Bách Khoa Tp.HCM. Tôi có thể giúp gì cho bạn?</t>
-  </si>
-  <si>
     <t>Xin chào, bạn là ai?</t>
   </si>
   <si>
-    <t>Điều kiện tốt nghiệp tiến sĩ?</t>
-  </si>
-  <si>
-    <t>Theo quy định của Trường ĐH Bách Khoa Tp.HCM,  điều kiện để nghiên cứu sinh được xét cấp bằng tiến sĩ là: 
-- Luận án của nghiên cứu sinh đã được Hội đồng đánh giá luận án cấp Trường thông qua đủ 90 ngày. 
-- Nghiên cứu sinh đã hoàn thành việc sửa đổi, bổ sung luận án theo Quyết nghị của Hội đồng đánh giá luận án tiến sĩ cấp Trường và được người hướng dẫn, Chủ tịch hội đồng, Phòng Đào tạo Sau đại học và nhà trường xác nhận. 
-- Nếu là trường hợp cần thẩm định theo thông báo của ĐHQG-HCM hoặc Bộ Giáo dục và Đào tạo thì kết quả thẩm định phải đạt yêu cầu theo Quy chế đào tạo tiến sĩ. 
-- Đã đăng trên trang thông tin điện tử của nhà trường và nộp Thư viện nhà trường, Thư viện ĐHQG-HCM, Thư viện Tổng hợp Thành phố Hồ Chí Minh (cả bản in và file pdf) toàn văn luận án và tóm tắt luận án hoàn chỉnh cuối cùng có chữ ký của nghiên cứu sinh, chữ ký của người hướng dẫn sau khi đã bổ sung, sửa chữa theo yêu cầu của Hội đồng đánh giá luận án cấp Trường và Hội đồng thẩm định (nếu có). Các tài liệu được đính kèm vào quyển toàn văn luận án bao gồm: + Quyết định thành lập và danh sách Hội đồng đánh giá luận án cấp Trường. + Quyết nghị của Hội đồng đánh giá luận án cấp Trường. + Bản giải trình các bổ sung, sửa chữa theo yêu cầu của Hội đồng đánh giá luận án cấp Trường và Hội đồng thẩm định (nếu có).</t>
+    <t>Xin chào, tôi là một trợ lý ảo hỗ trợ giải đáp các thắc mắc về quy định học vụ của trường ĐH Bách Khoa TP.HCM. Tôi có thể giúp gì cho bạn?</t>
   </si>
 </sst>
 </file>
@@ -560,7 +368,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B1000"/>
+  <dimension ref="A1:B978"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="51.54296875" customWidth="1"/>
@@ -572,200 +380,108 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>23</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="58" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="58" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="87" x14ac:dyDescent="0.35">
-      <c r="A8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="58" x14ac:dyDescent="0.35">
-      <c r="A11" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="145" x14ac:dyDescent="0.35">
-      <c r="A12" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="87" x14ac:dyDescent="0.35">
-      <c r="A13" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="159.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A15" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="174" x14ac:dyDescent="0.35">
-      <c r="A16" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="87" x14ac:dyDescent="0.35">
-      <c r="A17" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="101.5" x14ac:dyDescent="0.35">
-      <c r="A18" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="58" x14ac:dyDescent="0.35">
-      <c r="A19" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="58" x14ac:dyDescent="0.35">
-      <c r="A20" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="101.5" x14ac:dyDescent="0.35">
-      <c r="A21" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="174" x14ac:dyDescent="0.35">
-      <c r="A22" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A23" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A24" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="232" x14ac:dyDescent="0.35">
-      <c r="A25" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>49</v>
-      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" s="2"/>
@@ -4578,94 +4294,6 @@
     <row r="978" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A978" s="2"/>
       <c r="B978" s="2"/>
-    </row>
-    <row r="979" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A979" s="2"/>
-      <c r="B979" s="2"/>
-    </row>
-    <row r="980" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A980" s="2"/>
-      <c r="B980" s="2"/>
-    </row>
-    <row r="981" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A981" s="2"/>
-      <c r="B981" s="2"/>
-    </row>
-    <row r="982" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A982" s="2"/>
-      <c r="B982" s="2"/>
-    </row>
-    <row r="983" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A983" s="2"/>
-      <c r="B983" s="2"/>
-    </row>
-    <row r="984" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A984" s="2"/>
-      <c r="B984" s="2"/>
-    </row>
-    <row r="985" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A985" s="2"/>
-      <c r="B985" s="2"/>
-    </row>
-    <row r="986" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A986" s="2"/>
-      <c r="B986" s="2"/>
-    </row>
-    <row r="987" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A987" s="2"/>
-      <c r="B987" s="2"/>
-    </row>
-    <row r="988" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A988" s="2"/>
-      <c r="B988" s="2"/>
-    </row>
-    <row r="989" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A989" s="2"/>
-      <c r="B989" s="2"/>
-    </row>
-    <row r="990" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A990" s="2"/>
-      <c r="B990" s="2"/>
-    </row>
-    <row r="991" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A991" s="2"/>
-      <c r="B991" s="2"/>
-    </row>
-    <row r="992" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A992" s="2"/>
-      <c r="B992" s="2"/>
-    </row>
-    <row r="993" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A993" s="2"/>
-      <c r="B993" s="2"/>
-    </row>
-    <row r="994" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A994" s="2"/>
-      <c r="B994" s="2"/>
-    </row>
-    <row r="995" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A995" s="2"/>
-      <c r="B995" s="2"/>
-    </row>
-    <row r="996" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A996" s="2"/>
-      <c r="B996" s="2"/>
-    </row>
-    <row r="997" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A997" s="2"/>
-      <c r="B997" s="2"/>
-    </row>
-    <row r="998" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A998" s="2"/>
-      <c r="B998" s="2"/>
-    </row>
-    <row r="999" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A999" s="2"/>
-      <c r="B999" s="2"/>
-    </row>
-    <row r="1000" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1000" s="2"/>
-      <c r="B1000" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
